--- a/docs/architecture/nudge-category-vocabulary.xlsx
+++ b/docs/architecture/nudge-category-vocabulary.xlsx
@@ -39,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,8 +62,14 @@
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="009A3412"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -110,6 +116,11 @@
         <fgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEDD5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -137,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -184,6 +195,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -550,26 +564,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1">
+    <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
+          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). Auto-escalate: if this column has an entry, that pattern short-circuits the traffic light and jumps straight to Green (nudge now), like an ambulance through a red light — regardless of surrounding context. Leave Auto-escalate blank unless the item is time-critical. All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -589,10 +605,15 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>Auto-escalate</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -608,6 +629,7 @@
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -625,12 +647,13 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Illustrative only — panel replaces</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -645,7 +668,8 @@
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -660,7 +684,8 @@
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -675,7 +700,8 @@
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -690,7 +716,8 @@
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -705,7 +732,8 @@
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -720,7 +748,8 @@
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -735,60 +764,64 @@
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="7" t="inlineStr"/>
-      <c r="B12" s="7" t="inlineStr"/>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Worth paying attention to  (Yellow = watch)</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Sedation / RASS watch</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>“Still not waking” or oversedation talk</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr"/>
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="12" t="inlineStr"/>
+      <c r="B14" s="12" t="inlineStr"/>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr"/>
+      <c r="E14" s="12" t="inlineStr"/>
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -803,7 +836,8 @@
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr"/>
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -818,7 +852,8 @@
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr"/>
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -833,7 +868,8 @@
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -848,7 +884,8 @@
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr"/>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -863,7 +900,8 @@
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr"/>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -878,75 +916,80 @@
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="12" t="inlineStr"/>
-      <c r="B21" s="12" t="inlineStr"/>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="12" t="inlineStr"/>
-      <c r="B22" s="12" t="inlineStr"/>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr"/>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Less important — monitor only  (Red = stay quiet)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="15" t="n"/>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Routine neuro check cadence</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Stable exam, no new deficit mentioned</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr"/>
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Placeholder — stay quiet unless worsens</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="17" t="inlineStr"/>
+      <c r="B23" s="17" t="inlineStr"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr"/>
+      <c r="E23" s="17" t="inlineStr"/>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="17" t="inlineStr"/>
+      <c r="B24" s="17" t="inlineStr"/>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr"/>
+      <c r="E24" s="17" t="inlineStr"/>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -961,7 +1004,8 @@
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr"/>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr"/>
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -976,7 +1020,8 @@
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr"/>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr"/>
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -991,7 +1036,8 @@
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr"/>
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1006,7 +1052,8 @@
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr"/>
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1021,52 +1068,8 @@
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="17" t="inlineStr"/>
-      <c r="B30" s="17" t="inlineStr"/>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr"/>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="17" t="inlineStr"/>
-      <c r="B31" s="17" t="inlineStr"/>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr"/>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="17" t="inlineStr"/>
-      <c r="B32" s="17" t="inlineStr"/>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr"/>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr"/>
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1074,29 +1077,21 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C3:C32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C3:C29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Green,Yellow,Red"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F3:F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Draft,Reviewed,Approved"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;CCrisis Mirror — Nudge category vocabulary DRAFT</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -1106,26 +1101,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1">
+    <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
+          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). Auto-escalate: if this column has an entry, that pattern short-circuits the traffic light and jumps straight to Green (nudge now), like an ambulance through a red light — regardless of surrounding context. Leave Auto-escalate blank unless the item is time-critical. All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -1145,10 +1142,15 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>Auto-escalate</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1164,6 +1166,7 @@
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -1181,12 +1184,13 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Illustrative only</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1201,7 +1205,8 @@
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1216,7 +1221,8 @@
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1231,7 +1237,8 @@
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1246,7 +1253,8 @@
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1261,7 +1269,8 @@
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1276,7 +1285,8 @@
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1291,60 +1301,64 @@
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="7" t="inlineStr"/>
-      <c r="B12" s="7" t="inlineStr"/>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Worth paying attention to  (Yellow = watch)</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] DVT prophylaxis / skin watch</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Immobility without prophylaxis mentioned</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr"/>
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="12" t="inlineStr"/>
+      <c r="B14" s="12" t="inlineStr"/>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr"/>
+      <c r="E14" s="12" t="inlineStr"/>
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1359,7 +1373,8 @@
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr"/>
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1374,7 +1389,8 @@
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr"/>
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1389,7 +1405,8 @@
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1404,7 +1421,8 @@
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr"/>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1419,7 +1437,8 @@
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr"/>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1434,75 +1453,80 @@
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="12" t="inlineStr"/>
-      <c r="B21" s="12" t="inlineStr"/>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="12" t="inlineStr"/>
-      <c r="B22" s="12" t="inlineStr"/>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr"/>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Less important — monitor only  (Red = stay quiet)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="15" t="n"/>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Quiet on stable ortho postop</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Routine healing, no new pain/swelling</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr"/>
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Placeholder — stay quiet</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="17" t="inlineStr"/>
+      <c r="B23" s="17" t="inlineStr"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr"/>
+      <c r="E23" s="17" t="inlineStr"/>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="17" t="inlineStr"/>
+      <c r="B24" s="17" t="inlineStr"/>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr"/>
+      <c r="E24" s="17" t="inlineStr"/>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1517,7 +1541,8 @@
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr"/>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr"/>
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1532,7 +1557,8 @@
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr"/>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr"/>
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1547,7 +1573,8 @@
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr"/>
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1562,7 +1589,8 @@
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr"/>
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1577,52 +1605,8 @@
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="17" t="inlineStr"/>
-      <c r="B30" s="17" t="inlineStr"/>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr"/>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="17" t="inlineStr"/>
-      <c r="B31" s="17" t="inlineStr"/>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr"/>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="17" t="inlineStr"/>
-      <c r="B32" s="17" t="inlineStr"/>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr"/>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr"/>
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1630,29 +1614,21 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C3:C32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C3:C29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Green,Yellow,Red"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F3:F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Draft,Reviewed,Approved"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;CCrisis Mirror — Nudge category vocabulary DRAFT</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -1662,26 +1638,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1">
+    <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). All example rows are [PLACEHOLDER] only — not clinical guidance. Emergencies tab jump-off: Stanford Emergency Manual (Stanford Guide).</t>
+          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). Auto-escalate: if this column has an entry, that pattern short-circuits the traffic light and jumps straight to Green (nudge now), like an ambulance through a red light — regardless of surrounding context. Leave Auto-escalate blank unless the item is time-critical. All example rows are [PLACEHOLDER] only — not clinical guidance. Emergencies tab jump-off: Stanford Emergency Manual (Stanford Guide).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -1701,10 +1679,15 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>Auto-escalate</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1720,6 +1703,7 @@
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -1737,57 +1721,113 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>[PLACEHOLDER] Cardiac arrest — auto-escalate to Green on detection</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Jump-off: Stanford Emergency Manual — cardiac arrest. Replace with panel wording.</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="7" t="inlineStr"/>
-      <c r="B5" s="7" t="inlineStr"/>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="7" t="inlineStr"/>
-      <c r="B6" s="7" t="inlineStr"/>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="7" t="inlineStr"/>
-      <c r="B7" s="7" t="inlineStr"/>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>[PLACEHOLDER] Malignant hyperthermia short-circuit</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Unexpected hypercarbia / rigidity / fever under anesthesia</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>[PLACEHOLDER] Malignant hyperthermia — auto-escalate to Green on detection</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Jump-off: Stanford Emergency Manual — MH. Auto-escalate placeholder.</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>[PLACEHOLDER] Tension pneumothorax short-circuit</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Tension pneumothorax pattern in crisis talk</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>[PLACEHOLDER] Tension pneumothorax — auto-escalate to Green on detection</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Illustrative auto-escalate — panel replaces</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>[PLACEHOLDER] Airway obstruction / CICO short-circuit</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Cannot intubate cannot oxygenate / complete obstruction</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>[PLACEHOLDER] Airway obstruction — auto-escalate to Green on detection</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Jump-off: Stanford Emergency Manual — airway. Auto-escalate placeholder.</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1802,7 +1842,8 @@
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1817,7 +1858,8 @@
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1832,7 +1874,8 @@
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1847,7 +1890,8 @@
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1862,75 +1906,80 @@
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="7" t="inlineStr"/>
+      <c r="B13" s="7" t="inlineStr"/>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="7" t="inlineStr"/>
+      <c r="B14" s="7" t="inlineStr"/>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Worth paying attention to  (Yellow = watch)</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Difficult airway developing</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Repeated attempts / desatting but still oxygenating</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr"/>
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Jump-off: Stanford Emergency Manual — airway. Watch tier placeholder.</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="12" t="inlineStr"/>
-      <c r="B15" s="12" t="inlineStr"/>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="12" t="inlineStr"/>
-      <c r="B16" s="12" t="inlineStr"/>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1945,7 +1994,8 @@
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1960,7 +2010,8 @@
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr"/>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1975,7 +2026,8 @@
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr"/>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -1990,7 +2042,8 @@
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr"/>
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2005,7 +2058,8 @@
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr"/>
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2020,60 +2074,64 @@
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr"/>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="12" t="inlineStr"/>
+      <c r="B23" s="12" t="inlineStr"/>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr"/>
+      <c r="E23" s="12" t="inlineStr"/>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Less important — monitor only  (Red = stay quiet)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="15" t="n"/>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Post-event debrief note only</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>Crisis resolved; no new instability</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr"/>
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>Stanford Guide jump-off context — stay quiet unless recurrence. Placeholder.</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="17" t="inlineStr"/>
-      <c r="B25" s="17" t="inlineStr"/>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr"/>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="F25" s="16" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2088,7 +2146,8 @@
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr"/>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr"/>
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2103,7 +2162,8 @@
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr"/>
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2118,7 +2178,8 @@
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr"/>
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2133,7 +2194,8 @@
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr"/>
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2148,7 +2210,8 @@
         </is>
       </c>
       <c r="D30" s="17" t="inlineStr"/>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr"/>
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2163,7 +2226,8 @@
         </is>
       </c>
       <c r="D31" s="17" t="inlineStr"/>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr"/>
+      <c r="F31" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2178,7 +2242,8 @@
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr"/>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr"/>
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2186,29 +2251,21 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C3:C32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Green,Yellow,Red"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F3:F32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Draft,Reviewed,Approved"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;CCrisis Mirror — Nudge category vocabulary DRAFT</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -2218,26 +2275,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1">
+    <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
+          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). Auto-escalate: if this column has an entry, that pattern short-circuits the traffic light and jumps straight to Green (nudge now), like an ambulance through a red light — regardless of surrounding context. Leave Auto-escalate blank unless the item is time-critical. All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -2257,10 +2316,15 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>Auto-escalate</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2276,6 +2340,7 @@
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -2293,12 +2358,17 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>[PLACEHOLDER] Cardiac arrest / no pulse — auto-escalate to Green on detection</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Illustrative only</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2313,7 +2383,8 @@
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2328,7 +2399,8 @@
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2343,7 +2415,8 @@
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2358,7 +2431,8 @@
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2373,7 +2447,8 @@
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2388,7 +2463,8 @@
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2403,60 +2479,64 @@
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="7" t="inlineStr"/>
-      <c r="B12" s="7" t="inlineStr"/>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Worth paying attention to  (Yellow = watch)</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Suggest fluid bolus consideration</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Hypotension + “dry” talk without active bleed</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr"/>
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="12" t="inlineStr"/>
+      <c r="B14" s="12" t="inlineStr"/>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr"/>
+      <c r="E14" s="12" t="inlineStr"/>
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2471,7 +2551,8 @@
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr"/>
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2486,7 +2567,8 @@
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr"/>
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2501,7 +2583,8 @@
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2516,7 +2599,8 @@
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr"/>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2531,7 +2615,8 @@
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr"/>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2546,75 +2631,80 @@
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="12" t="inlineStr"/>
-      <c r="B21" s="12" t="inlineStr"/>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="12" t="inlineStr"/>
-      <c r="B22" s="12" t="inlineStr"/>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr"/>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Less important — monitor only  (Red = stay quiet)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="15" t="n"/>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Quiet on chronic compensated HF notes</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Stable chronic HF mentioned, no acute change</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr"/>
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Placeholder — stay quiet</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="17" t="inlineStr"/>
+      <c r="B23" s="17" t="inlineStr"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr"/>
+      <c r="E23" s="17" t="inlineStr"/>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="17" t="inlineStr"/>
+      <c r="B24" s="17" t="inlineStr"/>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr"/>
+      <c r="E24" s="17" t="inlineStr"/>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2629,7 +2719,8 @@
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr"/>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr"/>
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2644,7 +2735,8 @@
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr"/>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr"/>
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2659,7 +2751,8 @@
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr"/>
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2674,7 +2767,8 @@
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr"/>
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2689,52 +2783,8 @@
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="17" t="inlineStr"/>
-      <c r="B30" s="17" t="inlineStr"/>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr"/>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="17" t="inlineStr"/>
-      <c r="B31" s="17" t="inlineStr"/>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr"/>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="17" t="inlineStr"/>
-      <c r="B32" s="17" t="inlineStr"/>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr"/>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr"/>
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2742,29 +2792,21 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C3:C32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C3:C29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Green,Yellow,Red"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F3:F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Draft,Reviewed,Approved"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;CCrisis Mirror — Nudge category vocabulary DRAFT</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -2774,26 +2816,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1">
+    <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
+          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). Auto-escalate: if this column has an entry, that pattern short-circuits the traffic light and jumps straight to Green (nudge now), like an ambulance through a red light — regardless of surrounding context. Leave Auto-escalate blank unless the item is time-critical. All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -2813,10 +2857,15 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>Auto-escalate</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2832,6 +2881,7 @@
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -2849,27 +2899,49 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>[PLACEHOLDER] Airway obstruction — auto-escalate to Green on detection</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Illustrative only</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="7" t="inlineStr"/>
-      <c r="B5" s="7" t="inlineStr"/>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>[PLACEHOLDER] Tension pneumothorax short-circuit</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Tension pneumothorax / tracheal deviation / absent sounds + shock discussed</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>[PLACEHOLDER] Tension pneumothorax — auto-escalate to Green on detection</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Illustrative auto-escalate — panel replaces</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2884,7 +2956,8 @@
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2899,7 +2972,8 @@
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2914,7 +2988,8 @@
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2929,7 +3004,8 @@
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2944,7 +3020,8 @@
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2959,7 +3036,8 @@
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2974,7 +3052,8 @@
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2990,6 +3069,7 @@
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
@@ -3007,12 +3087,13 @@
           <t>Yellow</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr"/>
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3027,7 +3108,8 @@
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr"/>
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3042,7 +3124,8 @@
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr"/>
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3057,7 +3140,8 @@
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3072,7 +3156,8 @@
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr"/>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3087,7 +3172,8 @@
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr"/>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3102,7 +3188,8 @@
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr"/>
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3117,60 +3204,64 @@
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="12" t="inlineStr"/>
-      <c r="B22" s="12" t="inlineStr"/>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr"/>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Less important — monitor only  (Red = stay quiet)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="15" t="n"/>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Quiet on stable vent settings</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>No change in oxygenation discussed</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr"/>
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>Placeholder — stay quiet</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="17" t="inlineStr"/>
+      <c r="B24" s="17" t="inlineStr"/>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr"/>
+      <c r="E24" s="17" t="inlineStr"/>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3185,7 +3276,8 @@
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr"/>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr"/>
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3200,7 +3292,8 @@
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr"/>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr"/>
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3215,7 +3308,8 @@
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr"/>
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3230,7 +3324,8 @@
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr"/>
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3245,7 +3340,8 @@
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr"/>
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3260,37 +3356,8 @@
         </is>
       </c>
       <c r="D30" s="17" t="inlineStr"/>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="17" t="inlineStr"/>
-      <c r="B31" s="17" t="inlineStr"/>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr"/>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="17" t="inlineStr"/>
-      <c r="B32" s="17" t="inlineStr"/>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr"/>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr"/>
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3298,29 +3365,21 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A22:F22"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C3:C32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C3:C30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Green,Yellow,Red"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F3:F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Draft,Reviewed,Approved"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;CCrisis Mirror — Nudge category vocabulary DRAFT</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -3330,26 +3389,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1">
+    <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
+          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). Auto-escalate: if this column has an entry, that pattern short-circuits the traffic light and jumps straight to Green (nudge now), like an ambulance through a red light — regardless of surrounding context. Leave Auto-escalate blank unless the item is time-critical. All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -3369,10 +3430,15 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>Auto-escalate</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3388,6 +3454,7 @@
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -3405,12 +3472,13 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Illustrative only</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3425,7 +3493,8 @@
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3440,7 +3509,8 @@
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3455,7 +3525,8 @@
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3470,7 +3541,8 @@
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3485,7 +3557,8 @@
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3500,7 +3573,8 @@
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3515,60 +3589,64 @@
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="7" t="inlineStr"/>
-      <c r="B12" s="7" t="inlineStr"/>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Worth paying attention to  (Yellow = watch)</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Ileus / feeding pause watch</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Distension, vomiting, high residuals</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr"/>
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="12" t="inlineStr"/>
+      <c r="B14" s="12" t="inlineStr"/>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr"/>
+      <c r="E14" s="12" t="inlineStr"/>
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3583,7 +3661,8 @@
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr"/>
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3598,7 +3677,8 @@
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr"/>
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3613,7 +3693,8 @@
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3628,7 +3709,8 @@
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr"/>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3643,7 +3725,8 @@
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr"/>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3658,75 +3741,80 @@
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="12" t="inlineStr"/>
-      <c r="B21" s="12" t="inlineStr"/>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="12" t="inlineStr"/>
-      <c r="B22" s="12" t="inlineStr"/>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr"/>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Less important — monitor only  (Red = stay quiet)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="15" t="n"/>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Quiet on routine PPI already on</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Prophylaxis already confirmed</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr"/>
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Placeholder — stay quiet</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="17" t="inlineStr"/>
+      <c r="B23" s="17" t="inlineStr"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr"/>
+      <c r="E23" s="17" t="inlineStr"/>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="17" t="inlineStr"/>
+      <c r="B24" s="17" t="inlineStr"/>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr"/>
+      <c r="E24" s="17" t="inlineStr"/>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3741,7 +3829,8 @@
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr"/>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr"/>
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3756,7 +3845,8 @@
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr"/>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr"/>
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3771,7 +3861,8 @@
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr"/>
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3786,7 +3877,8 @@
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr"/>
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3801,52 +3893,8 @@
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="17" t="inlineStr"/>
-      <c r="B30" s="17" t="inlineStr"/>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr"/>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="17" t="inlineStr"/>
-      <c r="B31" s="17" t="inlineStr"/>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr"/>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="17" t="inlineStr"/>
-      <c r="B32" s="17" t="inlineStr"/>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr"/>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr"/>
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3854,29 +3902,21 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C3:C32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C3:C29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Green,Yellow,Red"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F3:F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Draft,Reviewed,Approved"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;CCrisis Mirror — Nudge category vocabulary DRAFT</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -3886,26 +3926,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1">
+    <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
+          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). Auto-escalate: if this column has an entry, that pattern short-circuits the traffic light and jumps straight to Green (nudge now), like an ambulance through a red light — regardless of surrounding context. Leave Auto-escalate blank unless the item is time-critical. All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -3925,10 +3967,15 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>Auto-escalate</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3944,6 +3991,7 @@
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -3961,12 +4009,13 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Illustrative only</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3981,7 +4030,8 @@
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -3996,7 +4046,8 @@
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4011,7 +4062,8 @@
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4026,7 +4078,8 @@
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4041,7 +4094,8 @@
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4056,7 +4110,8 @@
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4071,60 +4126,64 @@
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="7" t="inlineStr"/>
-      <c r="B12" s="7" t="inlineStr"/>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Worth paying attention to  (Yellow = watch)</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Encephalopathy precautions</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Confusion + known liver disease</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr"/>
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="12" t="inlineStr"/>
+      <c r="B14" s="12" t="inlineStr"/>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr"/>
+      <c r="E14" s="12" t="inlineStr"/>
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4139,7 +4198,8 @@
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr"/>
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4154,7 +4214,8 @@
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr"/>
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4169,7 +4230,8 @@
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4184,7 +4246,8 @@
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr"/>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4199,7 +4262,8 @@
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr"/>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4214,75 +4278,80 @@
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="12" t="inlineStr"/>
-      <c r="B21" s="12" t="inlineStr"/>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="12" t="inlineStr"/>
-      <c r="B22" s="12" t="inlineStr"/>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr"/>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Less important — monitor only  (Red = stay quiet)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="15" t="n"/>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Quiet on stable compensated cirrhosis</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>No new decompensation discussed</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr"/>
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Placeholder — stay quiet</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="17" t="inlineStr"/>
+      <c r="B23" s="17" t="inlineStr"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr"/>
+      <c r="E23" s="17" t="inlineStr"/>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="17" t="inlineStr"/>
+      <c r="B24" s="17" t="inlineStr"/>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr"/>
+      <c r="E24" s="17" t="inlineStr"/>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4297,7 +4366,8 @@
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr"/>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr"/>
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4312,7 +4382,8 @@
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr"/>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr"/>
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4327,7 +4398,8 @@
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr"/>
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4342,7 +4414,8 @@
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr"/>
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4357,52 +4430,8 @@
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="17" t="inlineStr"/>
-      <c r="B30" s="17" t="inlineStr"/>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr"/>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="17" t="inlineStr"/>
-      <c r="B31" s="17" t="inlineStr"/>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr"/>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="17" t="inlineStr"/>
-      <c r="B32" s="17" t="inlineStr"/>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr"/>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr"/>
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4410,29 +4439,21 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C3:C32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C3:C29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Green,Yellow,Red"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F3:F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Draft,Reviewed,Approved"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;CCrisis Mirror — Nudge category vocabulary DRAFT</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -4442,26 +4463,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1">
+    <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
+          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). Auto-escalate: if this column has an entry, that pattern short-circuits the traffic light and jumps straight to Green (nudge now), like an ambulance through a red light — regardless of surrounding context. Leave Auto-escalate blank unless the item is time-critical. All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -4481,10 +4504,15 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>Auto-escalate</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -4500,6 +4528,7 @@
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -4517,12 +4546,13 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Illustrative only</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4537,7 +4567,8 @@
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4552,7 +4583,8 @@
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4567,7 +4599,8 @@
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4582,7 +4615,8 @@
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4597,7 +4631,8 @@
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4612,7 +4647,8 @@
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4627,60 +4663,64 @@
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="7" t="inlineStr"/>
-      <c r="B12" s="7" t="inlineStr"/>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Worth paying attention to  (Yellow = watch)</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Nephrotoxin / creatinine watch</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Rising Cr + nephrotoxin mentioned</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr"/>
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="12" t="inlineStr"/>
+      <c r="B14" s="12" t="inlineStr"/>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr"/>
+      <c r="E14" s="12" t="inlineStr"/>
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4695,7 +4735,8 @@
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr"/>
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4710,7 +4751,8 @@
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr"/>
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4725,7 +4767,8 @@
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4740,7 +4783,8 @@
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr"/>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4755,7 +4799,8 @@
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr"/>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4770,75 +4815,80 @@
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="12" t="inlineStr"/>
-      <c r="B21" s="12" t="inlineStr"/>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="12" t="inlineStr"/>
-      <c r="B22" s="12" t="inlineStr"/>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr"/>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Less important — monitor only  (Red = stay quiet)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="15" t="n"/>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Quiet on stable CKD baseline</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Creatinine at known baseline, no change</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr"/>
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Placeholder — stay quiet</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="17" t="inlineStr"/>
+      <c r="B23" s="17" t="inlineStr"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr"/>
+      <c r="E23" s="17" t="inlineStr"/>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="17" t="inlineStr"/>
+      <c r="B24" s="17" t="inlineStr"/>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr"/>
+      <c r="E24" s="17" t="inlineStr"/>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4853,7 +4903,8 @@
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr"/>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr"/>
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4868,7 +4919,8 @@
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr"/>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr"/>
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4883,7 +4935,8 @@
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr"/>
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4898,7 +4951,8 @@
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr"/>
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4913,52 +4967,8 @@
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="17" t="inlineStr"/>
-      <c r="B30" s="17" t="inlineStr"/>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr"/>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="17" t="inlineStr"/>
-      <c r="B31" s="17" t="inlineStr"/>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr"/>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="17" t="inlineStr"/>
-      <c r="B32" s="17" t="inlineStr"/>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr"/>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr"/>
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -4966,29 +4976,21 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C3:C32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C3:C29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Green,Yellow,Red"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F3:F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Draft,Reviewed,Approved"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;CCrisis Mirror — Nudge category vocabulary DRAFT</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -4998,26 +5000,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1">
+    <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
+          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). Auto-escalate: if this column has an entry, that pattern short-circuits the traffic light and jumps straight to Green (nudge now), like an ambulance through a red light — regardless of surrounding context. Leave Auto-escalate blank unless the item is time-critical. All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -5037,10 +5041,15 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>Auto-escalate</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -5056,6 +5065,7 @@
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -5073,12 +5083,13 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Illustrative only</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5093,7 +5104,8 @@
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5108,7 +5120,8 @@
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5123,7 +5136,8 @@
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5138,7 +5152,8 @@
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5153,7 +5168,8 @@
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5168,7 +5184,8 @@
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5183,60 +5200,64 @@
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="7" t="inlineStr"/>
-      <c r="B12" s="7" t="inlineStr"/>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Worth paying attention to  (Yellow = watch)</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Transfusion threshold watch</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Hb near institutional threshold</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr"/>
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="12" t="inlineStr"/>
+      <c r="B14" s="12" t="inlineStr"/>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr"/>
+      <c r="E14" s="12" t="inlineStr"/>
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5251,7 +5272,8 @@
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr"/>
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5266,7 +5288,8 @@
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr"/>
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5281,7 +5304,8 @@
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5296,7 +5320,8 @@
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr"/>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5311,7 +5336,8 @@
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr"/>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5326,75 +5352,80 @@
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="12" t="inlineStr"/>
-      <c r="B21" s="12" t="inlineStr"/>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="12" t="inlineStr"/>
-      <c r="B22" s="12" t="inlineStr"/>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr"/>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Less important — monitor only  (Red = stay quiet)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="15" t="n"/>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Quiet on stable chronic anemia</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Known chronic anemia, no acute drop</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr"/>
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Placeholder — stay quiet</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="17" t="inlineStr"/>
+      <c r="B23" s="17" t="inlineStr"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr"/>
+      <c r="E23" s="17" t="inlineStr"/>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="17" t="inlineStr"/>
+      <c r="B24" s="17" t="inlineStr"/>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr"/>
+      <c r="E24" s="17" t="inlineStr"/>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5409,7 +5440,8 @@
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr"/>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr"/>
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5424,7 +5456,8 @@
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr"/>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr"/>
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5439,7 +5472,8 @@
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr"/>
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5454,7 +5488,8 @@
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr"/>
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5469,52 +5504,8 @@
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="17" t="inlineStr"/>
-      <c r="B30" s="17" t="inlineStr"/>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr"/>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="17" t="inlineStr"/>
-      <c r="B31" s="17" t="inlineStr"/>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr"/>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="17" t="inlineStr"/>
-      <c r="B32" s="17" t="inlineStr"/>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr"/>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr"/>
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5522,29 +5513,21 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C3:C32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C3:C29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Green,Yellow,Red"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F3:F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Draft,Reviewed,Approved"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;CCrisis Mirror — Nudge category vocabulary DRAFT</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -5554,26 +5537,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1">
+    <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
+          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). Auto-escalate: if this column has an entry, that pattern short-circuits the traffic light and jumps straight to Green (nudge now), like an ambulance through a red light — regardless of surrounding context. Leave Auto-escalate blank unless the item is time-critical. All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -5593,10 +5578,15 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>Auto-escalate</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -5612,6 +5602,7 @@
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -5629,12 +5620,13 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Illustrative only</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5649,7 +5641,8 @@
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5664,7 +5657,8 @@
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5679,7 +5673,8 @@
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5694,7 +5689,8 @@
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5709,7 +5705,8 @@
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5724,7 +5721,8 @@
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5739,60 +5737,64 @@
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="7" t="inlineStr"/>
-      <c r="B12" s="7" t="inlineStr"/>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Worth paying attention to  (Yellow = watch)</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Source control / culture plan watch</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Fever with undrained collection discussed</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr"/>
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="12" t="inlineStr"/>
+      <c r="B14" s="12" t="inlineStr"/>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr"/>
+      <c r="E14" s="12" t="inlineStr"/>
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5807,7 +5809,8 @@
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr"/>
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5822,7 +5825,8 @@
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr"/>
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5837,7 +5841,8 @@
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5852,7 +5857,8 @@
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr"/>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5867,7 +5873,8 @@
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr"/>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5882,75 +5889,80 @@
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="12" t="inlineStr"/>
-      <c r="B21" s="12" t="inlineStr"/>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="12" t="inlineStr"/>
-      <c r="B22" s="12" t="inlineStr"/>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr"/>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Less important — monitor only  (Red = stay quiet)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="15" t="n"/>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Quiet on completed antibiotic course</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Course finished, cultures negative, stable</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr"/>
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Placeholder — stay quiet</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="17" t="inlineStr"/>
+      <c r="B23" s="17" t="inlineStr"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr"/>
+      <c r="E23" s="17" t="inlineStr"/>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="17" t="inlineStr"/>
+      <c r="B24" s="17" t="inlineStr"/>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr"/>
+      <c r="E24" s="17" t="inlineStr"/>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5965,7 +5977,8 @@
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr"/>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr"/>
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5980,7 +5993,8 @@
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr"/>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr"/>
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -5995,7 +6009,8 @@
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr"/>
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6010,7 +6025,8 @@
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr"/>
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6025,52 +6041,8 @@
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="17" t="inlineStr"/>
-      <c r="B30" s="17" t="inlineStr"/>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr"/>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="17" t="inlineStr"/>
-      <c r="B31" s="17" t="inlineStr"/>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr"/>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="17" t="inlineStr"/>
-      <c r="B32" s="17" t="inlineStr"/>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr"/>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr"/>
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6078,29 +6050,21 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C3:C32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C3:C29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Green,Yellow,Red"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F3:F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Draft,Reviewed,Approved"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;CCrisis Mirror — Nudge category vocabulary DRAFT</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -6110,26 +6074,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1">
+    <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
+          <t>Legend (traffic-light framing): Green = Extremely important — escalate (nudge now). Yellow = Worth paying attention to (watch). Red = Less important — monitor only (stay quiet). Auto-escalate: if this column has an entry, that pattern short-circuits the traffic light and jumps straight to Green (nudge now), like an ambulance through a red light — regardless of surrounding context. Leave Auto-escalate blank unless the item is time-critical. All example rows are [PLACEHOLDER] only — not clinical guidance.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -6149,10 +6115,15 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>Auto-escalate</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -6168,6 +6139,7 @@
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -6185,12 +6157,13 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Illustrative only</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6205,7 +6178,8 @@
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6220,7 +6194,8 @@
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6235,7 +6210,8 @@
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6250,7 +6226,8 @@
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6265,7 +6242,8 @@
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6280,7 +6258,8 @@
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6295,60 +6274,64 @@
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="7" t="inlineStr"/>
-      <c r="B12" s="7" t="inlineStr"/>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Worth paying attention to  (Yellow = watch)</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Glucose target / insulin drip watch</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Repeated highs or lows discussed</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr"/>
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="12" t="inlineStr"/>
+      <c r="B14" s="12" t="inlineStr"/>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr"/>
+      <c r="E14" s="12" t="inlineStr"/>
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6363,7 +6346,8 @@
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr"/>
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6378,7 +6362,8 @@
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr"/>
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6393,7 +6378,8 @@
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6408,7 +6394,8 @@
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr"/>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6423,7 +6410,8 @@
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr"/>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6438,75 +6426,80 @@
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="12" t="inlineStr"/>
-      <c r="B21" s="12" t="inlineStr"/>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="12" t="inlineStr"/>
-      <c r="B22" s="12" t="inlineStr"/>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr"/>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Less important — monitor only  (Red = stay quiet)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="15" t="n"/>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>[PLACEHOLDER] Quiet on stable controlled diabetes</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Glucose in target, no titration talk</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr"/>
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Placeholder — stay quiet</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="17" t="inlineStr"/>
+      <c r="B23" s="17" t="inlineStr"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr"/>
+      <c r="E23" s="17" t="inlineStr"/>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="17" t="inlineStr"/>
+      <c r="B24" s="17" t="inlineStr"/>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr"/>
+      <c r="E24" s="17" t="inlineStr"/>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6521,7 +6514,8 @@
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr"/>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr"/>
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6536,7 +6530,8 @@
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr"/>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr"/>
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6551,7 +6546,8 @@
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr"/>
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6566,7 +6562,8 @@
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr"/>
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6581,52 +6578,8 @@
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="17" t="inlineStr"/>
-      <c r="B30" s="17" t="inlineStr"/>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr"/>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="17" t="inlineStr"/>
-      <c r="B31" s="17" t="inlineStr"/>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr"/>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="17" t="inlineStr"/>
-      <c r="B32" s="17" t="inlineStr"/>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr"/>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr"/>
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -6634,28 +6587,20 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C3:C32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C3:C29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Green,Yellow,Red"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F3:F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Draft,Reviewed,Approved"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;CCrisis Mirror — Nudge category vocabulary DRAFT</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>